--- a/datos/B Completo revistas.xlsx
+++ b/datos/B Completo revistas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorge/Desktop/AUTOESCUELA/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0EC31D-FA69-ED43-84FE-6657AE5A50A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAEFA5C-4610-2347-8949-95A645D2D19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="23220" windowHeight="16820" xr2:uid="{AE6512D7-AD52-4543-8CDE-87DCF5042393}"/>
   </bookViews>
@@ -422,25 +422,25 @@
     <t>imagenes/furgomal.png</t>
   </si>
   <si>
-    <t>imágenes/semaforcru.png</t>
-  </si>
-  <si>
-    <t>imágenes/ciclo31.png</t>
-  </si>
-  <si>
-    <t>imágenes/curvass.png</t>
-  </si>
-  <si>
-    <t>imágenes/curvar.png</t>
-  </si>
-  <si>
-    <t>imágenes/dangecur.png</t>
-  </si>
-  <si>
     <t>6. Al adelantar al ciclista que aparece en la fotografía, ¿es obligatorio invadir el carril de sentido contrario de la calzada?</t>
   </si>
   <si>
     <t>C) Sí</t>
+  </si>
+  <si>
+    <t>imagenes/semaforcru.png</t>
+  </si>
+  <si>
+    <t>imagenes/curvass.png</t>
+  </si>
+  <si>
+    <t>imagenes/ciclo31.png</t>
+  </si>
+  <si>
+    <t>imagenes/curvar.png</t>
+  </si>
+  <si>
+    <t>imagenes/dangecur.png</t>
   </si>
 </sst>
 </file>
@@ -936,7 +936,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
@@ -945,7 +945,7 @@
         <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
         <v>121</v>
@@ -1130,7 +1130,7 @@
         <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -1235,7 +1235,7 @@
         <v>121</v>
       </c>
       <c r="F23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -1255,7 +1255,7 @@
         <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -1343,7 +1343,7 @@
         <v>121</v>
       </c>
       <c r="F29" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -1380,7 +1380,7 @@
         <v>121</v>
       </c>
       <c r="F31" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="104" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
